--- a/Result/profitability/9919.xlsx
+++ b/Result/profitability/9919.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4637499999999999</v>
+        <v>-0.4899999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>7.74</v>
+        <v>7.046250000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.21</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3624999999999999</v>
+        <v>-0.4124999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>9.164999999999999</v>
+        <v>8.258749999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.23</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2824999999999999</v>
+        <v>-0.4149999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>10.20875</v>
+        <v>9.72125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2974999999999999</v>
+        <v>-0.2987499999999998</v>
       </c>
       <c r="N5" t="n">
-        <v>11.54125</v>
+        <v>11.43625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.35</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1537499999999999</v>
+        <v>-0.1374999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>13.87875</v>
+        <v>14.2325</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02500000000000011</v>
+        <v>0.0412500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>16.80125</v>
+        <v>17.66625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.65</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2237500000000001</v>
+        <v>0.1875000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>20.645</v>
+        <v>19.91125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9919</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>639</v>
+      </c>
+      <c r="D75" t="n">
+        <v>615</v>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-154</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-24.07%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-159</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-158</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.5962499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.4775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5576923076923077</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.870000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.6089211618257262</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.01000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.01249999999999996</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.8400000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1822125813449025</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
